--- a/Documentation/Best For Weighting Tables/Best Budget Friendly Pets.xlsx
+++ b/Documentation/Best For Weighting Tables/Best Budget Friendly Pets.xlsx
@@ -8,12 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tim Thomasson\Interactive-Pet-Marketplace\Documentation\Best For Weighting Tables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0B44003E-C706-48A9-BA5E-355B212D4DDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{924F6F3C-67E6-4DF8-BDBF-5435A9DE6E93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3960" yWindow="2430" windowWidth="21600" windowHeight="11295" xr2:uid="{D6C346F5-4D4D-4F05-AAEE-3DCAE15AF7C2}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{D6C346F5-4D4D-4F05-AAEE-3DCAE15AF7C2}"/>
   </bookViews>
   <sheets>
     <sheet name="Best Budget Friendly Pets_x0009_" sheetId="1" r:id="rId1"/>
+    <sheet name="Filters" sheetId="2" r:id="rId2"/>
+    <sheet name="Lists" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="18">
   <si>
     <t>Feature</t>
   </si>
@@ -59,9 +61,6 @@
     <t>Price tier</t>
   </si>
   <si>
-    <t>Price Category=Budget Friendly</t>
-  </si>
-  <si>
     <t>Return / gift suitability</t>
   </si>
   <si>
@@ -75,6 +74,27 @@
   </si>
   <si>
     <t>Value for money</t>
+  </si>
+  <si>
+    <t>Filter</t>
+  </si>
+  <si>
+    <t>Value</t>
+  </si>
+  <si>
+    <t>equal</t>
+  </si>
+  <si>
+    <t>not equal</t>
+  </si>
+  <si>
+    <t>less thatn</t>
+  </si>
+  <si>
+    <t>greater than</t>
+  </si>
+  <si>
+    <t>Budget Friendly</t>
   </si>
 </sst>
 </file>
@@ -118,7 +138,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -135,6 +155,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -469,7 +490,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{859346F0-3DC9-4E8D-87FD-C9CBF27A40DC}">
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:B9"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="32.42578125" style="3" bestFit="1" customWidth="1"/>
@@ -511,10 +532,10 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5" s="2" t="s">
         <v>6</v>
+      </c>
+      <c r="B5" s="4">
+        <v>0.05</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -522,7 +543,7 @@
         <v>7</v>
       </c>
       <c r="B6" s="4">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
@@ -546,15 +567,89 @@
         <v>10</v>
       </c>
       <c r="B9" s="4">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="3" t="s">
+        <v>0.3</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A2C766BB-A990-47C5-BFF2-00B059108E78}">
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="18" customWidth="1"/>
+    <col min="2" max="2" width="20.140625" customWidth="1"/>
+    <col min="3" max="3" width="14.5703125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="B10" s="4">
-        <v>0.3</v>
+      <c r="B1" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{A1D0E9E5-8409-4DAB-97DC-87363DCFCC23}">
+          <x14:formula1>
+            <xm:f>Lists!$A$1:$A$4</xm:f>
+          </x14:formula1>
+          <xm:sqref>B1:B1048576</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{22518B82-0645-45AD-8EEB-3DDAF318F397}">
+  <dimension ref="A1:A4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="13.85546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>16</v>
       </c>
     </row>
   </sheetData>

--- a/Documentation/Best For Weighting Tables/Best Budget Friendly Pets.xlsx
+++ b/Documentation/Best For Weighting Tables/Best Budget Friendly Pets.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tim Thomasson\Interactive-Pet-Marketplace\Documentation\Best For Weighting Tables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{924F6F3C-67E6-4DF8-BDBF-5435A9DE6E93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D45EF449-32C4-40DC-879B-794B67987B4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{D6C346F5-4D4D-4F05-AAEE-3DCAE15AF7C2}"/>
   </bookViews>
@@ -58,9 +58,6 @@
     <t>Maintenance requirements</t>
   </si>
   <si>
-    <t>Price tier</t>
-  </si>
-  <si>
     <t>Return / gift suitability</t>
   </si>
   <si>
@@ -95,6 +92,9 @@
   </si>
   <si>
     <t>Budget Friendly</t>
+  </si>
+  <si>
+    <t>Price Category</t>
   </si>
 </sst>
 </file>
@@ -532,7 +532,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B5" s="4">
         <v>0.05</v>
@@ -540,7 +540,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B6" s="4">
         <v>0.1</v>
@@ -548,7 +548,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B7" s="4">
         <v>0.1</v>
@@ -556,7 +556,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B8" s="4">
         <v>0.1</v>
@@ -564,7 +564,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B9" s="4">
         <v>0.3</v>
@@ -587,24 +587,24 @@
   <sheetData>
     <row r="1" spans="1:3" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1" s="6" t="s">
         <v>11</v>
-      </c>
-      <c r="B1" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="C1" s="6" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="B2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
   </sheetData>
@@ -634,22 +634,22 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>
